--- a/TimeTable (1).xlsx
+++ b/TimeTable (1).xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New_Anand_Files\Dhara_pvd_decor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New_Anand_Files\Dhara_pvd_decor\backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5772" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
   <si>
     <t>brand_mast</t>
   </si>
@@ -164,9 +164,6 @@
     <t>completed</t>
   </si>
   <si>
-    <t>Working</t>
-  </si>
-  <si>
     <t>days</t>
   </si>
   <si>
@@ -255,12 +252,60 @@
   </si>
   <si>
     <t>research and dropdown in column Minor changes and enhancements in country page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">validations and research </t>
+  </si>
+  <si>
+    <t>16/12/25</t>
+  </si>
+  <si>
+    <t>Did research, bug fixing, validation and final testin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">did some changes and thinking </t>
+  </si>
+  <si>
+    <t>starttime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endtime </t>
+  </si>
+  <si>
+    <t>working on finyeargrid ts and html css</t>
+  </si>
+  <si>
+    <t>app-finyear-grid</t>
+  </si>
+  <si>
+    <t>excel timesheet and alospushed some code and updated some things</t>
+  </si>
+  <si>
+    <t>Created the finyear grid and also coded the html ts and css code required more time as needed to changein bothts and css for grid column layout</t>
+  </si>
+  <si>
+    <t>app-edit-finyear</t>
+  </si>
+  <si>
+    <t>careted insert andupdate formalsocomplted the coding of css and html and ts partialas iencountred a bug of utc</t>
+  </si>
+  <si>
+    <t>17/12/25</t>
+  </si>
+  <si>
+    <t>API/SP changes</t>
+  </si>
+  <si>
+    <t>solved the bug of the date and also soved in both insert and updtatecaseadded new autogenerate forfin year and also pushed the code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm\ AM/PM;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -313,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -327,11 +372,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,409 +670,338 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="14.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="35.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="8">
+        <v>72</v>
+      </c>
+      <c r="E2" s="7">
         <v>1.5</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F2" s="11"/>
+      <c r="H2" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="H3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="H4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="H5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="H6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="F6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="H7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="H8" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>72</v>
+    </row>
+    <row r="9" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="9">
+        <v>4</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.8125</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0.40625</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0.52083333333333337</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1042,10 +1028,10 @@
         <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1059,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1073,7 +1059,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1087,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1101,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1115,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1129,7 +1115,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1137,13 +1123,28 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1308,6 +1309,232 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1327,7 +1554,7 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="8"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1335,7 +1562,7 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1343,7 +1570,7 @@
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1351,7 +1578,7 @@
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="6"/>
     </row>
   </sheetData>
